--- a/output/Data and Chart Outputs/cameroon_arsel_energy_balance.xlsx
+++ b/output/Data and Chart Outputs/cameroon_arsel_energy_balance.xlsx
@@ -189,12 +189,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$10</f>
+              <f>'Chart'!$A$2:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$B$2:$B$10</f>
+              <f>'Chart'!$B$2:$B$13</f>
             </numRef>
           </val>
         </ser>
@@ -217,12 +217,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$10</f>
+              <f>'Chart'!$A$2:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$C$2:$C$10</f>
+              <f>'Chart'!$C$2:$C$13</f>
             </numRef>
           </val>
         </ser>
@@ -245,12 +245,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$10</f>
+              <f>'Chart'!$A$2:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$D$2:$D$10</f>
+              <f>'Chart'!$D$2:$D$13</f>
             </numRef>
           </val>
         </ser>
@@ -273,12 +273,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$10</f>
+              <f>'Chart'!$A$2:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$E$2:$E$10</f>
+              <f>'Chart'!$E$2:$E$13</f>
             </numRef>
           </val>
         </ser>
@@ -301,12 +301,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$10</f>
+              <f>'Chart'!$A$2:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$F$2:$F$10</f>
+              <f>'Chart'!$F$2:$F$13</f>
             </numRef>
           </val>
         </ser>
@@ -329,12 +329,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$10</f>
+              <f>'Chart'!$A$2:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$G$2:$G$10</f>
+              <f>'Chart'!$G$2:$G$13</f>
             </numRef>
           </val>
         </ser>
@@ -357,12 +357,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$10</f>
+              <f>'Chart'!$A$2:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$H$2:$H$10</f>
+              <f>'Chart'!$H$2:$H$13</f>
             </numRef>
           </val>
         </ser>
@@ -385,12 +385,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$10</f>
+              <f>'Chart'!$A$2:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$I$2:$I$10</f>
+              <f>'Chart'!$I$2:$I$13</f>
             </numRef>
           </val>
         </ser>
@@ -527,12 +527,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart - Injections vs off-take'!$A$2:$A$10</f>
+              <f>'Chart - Injections vs off-take'!$A$2:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - Injections vs off-take'!$B$2:$B$10</f>
+              <f>'Chart - Injections vs off-take'!$B$2:$B$13</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -563,12 +563,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart - Injections vs off-take'!$A$2:$A$10</f>
+              <f>'Chart - Injections vs off-take'!$A$2:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - Injections vs off-take'!$C$2:$C$10</f>
+              <f>'Chart - Injections vs off-take'!$C$2:$C$13</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -698,12 +698,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart - HT customers'!$A$2:$A$10</f>
+              <f>'Chart - HT customers'!$A$2:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - HT customers'!$B$2:$B$10</f>
+              <f>'Chart - HT customers'!$B$2:$B$13</f>
             </numRef>
           </val>
         </ser>
@@ -726,12 +726,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart - HT customers'!$A$2:$A$10</f>
+              <f>'Chart - HT customers'!$A$2:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - HT customers'!$C$2:$C$10</f>
+              <f>'Chart - HT customers'!$C$2:$C$13</f>
             </numRef>
           </val>
         </ser>
@@ -754,12 +754,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart - HT customers'!$A$2:$A$10</f>
+              <f>'Chart - HT customers'!$A$2:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - HT customers'!$D$2:$D$10</f>
+              <f>'Chart - HT customers'!$D$2:$D$13</f>
             </numRef>
           </val>
         </ser>
@@ -782,12 +782,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart - HT customers'!$A$2:$A$10</f>
+              <f>'Chart - HT customers'!$A$2:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - HT customers'!$E$2:$E$10</f>
+              <f>'Chart - HT customers'!$E$2:$E$13</f>
             </numRef>
           </val>
         </ser>
@@ -810,12 +810,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart - HT customers'!$A$2:$A$10</f>
+              <f>'Chart - HT customers'!$A$2:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - HT customers'!$F$2:$F$10</f>
+              <f>'Chart - HT customers'!$F$2:$F$13</f>
             </numRef>
           </val>
         </ser>
@@ -1385,7 +1385,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1527,175 +1527,262 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>45778</v>
+        <v>45748</v>
       </c>
       <c r="B5" t="n">
-        <v>218.458</v>
+        <v>211.461</v>
       </c>
       <c r="C5" t="n">
-        <v>128.581164</v>
+        <v>156.53831</v>
       </c>
       <c r="D5" t="n">
-        <v>77.03</v>
+        <v>75.41500000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>73.521</v>
+        <v>62.194</v>
       </c>
       <c r="F5" t="n">
-        <v>75.678</v>
+        <v>43.505</v>
       </c>
       <c r="G5" t="n">
-        <v>34.79385</v>
+        <v>38.6016</v>
       </c>
       <c r="H5" t="n">
-        <v>1.23886</v>
+        <v>6.08966</v>
       </c>
       <c r="I5" t="n">
-        <v>5.245</v>
+        <v>5.155</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>45809</v>
+        <v>45778</v>
       </c>
       <c r="B6" t="n">
-        <v>215.673</v>
+        <v>218.458</v>
       </c>
       <c r="C6" t="n">
-        <v>124.234705</v>
+        <v>128.581164</v>
       </c>
       <c r="D6" t="n">
-        <v>85.56</v>
+        <v>77.03</v>
       </c>
       <c r="E6" t="n">
-        <v>71.702</v>
+        <v>73.521</v>
       </c>
       <c r="F6" t="n">
-        <v>56.997</v>
+        <v>75.678</v>
       </c>
       <c r="G6" t="n">
-        <v>26.88844</v>
+        <v>34.79385</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>1.23886</v>
       </c>
       <c r="I6" t="n">
-        <v>3.844</v>
+        <v>5.245</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>45839</v>
+        <v>45809</v>
       </c>
       <c r="B7" t="n">
-        <v>200.388</v>
+        <v>215.673</v>
       </c>
       <c r="C7" t="n">
-        <v>144.213379</v>
+        <v>124.234705</v>
       </c>
       <c r="D7" t="n">
-        <v>89.746</v>
+        <v>85.56</v>
       </c>
       <c r="E7" t="n">
-        <v>52.55</v>
+        <v>71.702</v>
       </c>
       <c r="F7" t="n">
-        <v>60.451</v>
+        <v>56.997</v>
       </c>
       <c r="G7" t="n">
-        <v>22.69423</v>
+        <v>26.88844</v>
       </c>
       <c r="H7" t="n">
-        <v>0.75806</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>2.043</v>
+        <v>3.844</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>45901</v>
+        <v>45839</v>
       </c>
       <c r="B8" t="n">
-        <v>205.416</v>
+        <v>200.388</v>
       </c>
       <c r="C8" t="n">
-        <v>200.394719</v>
+        <v>144.213379</v>
       </c>
       <c r="D8" t="n">
-        <v>76.643</v>
+        <v>89.746</v>
       </c>
       <c r="E8" t="n">
-        <v>9.42</v>
+        <v>52.55</v>
       </c>
       <c r="F8" t="n">
-        <v>40.297</v>
+        <v>60.451</v>
       </c>
       <c r="G8" t="n">
-        <v>33.73237</v>
+        <v>22.69423</v>
       </c>
       <c r="H8" t="n">
-        <v>2.61244</v>
+        <v>0.75806</v>
       </c>
       <c r="I8" t="n">
-        <v>1.684</v>
+        <v>2.043</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>45962</v>
+        <v>45870</v>
       </c>
       <c r="B9" t="n">
-        <v>207.845</v>
+        <v>193.413</v>
       </c>
       <c r="C9" t="n">
-        <v>163.010029</v>
+        <v>190.294783</v>
       </c>
       <c r="D9" t="n">
-        <v>85.893</v>
+        <v>77.164</v>
       </c>
       <c r="E9" t="n">
-        <v>45.654</v>
+        <v>21.961</v>
       </c>
       <c r="F9" t="n">
-        <v>56.861</v>
+        <v>51.31</v>
       </c>
       <c r="G9" t="n">
-        <v>32.26926</v>
+        <v>31.02929</v>
       </c>
       <c r="H9" t="n">
-        <v>6.15653</v>
+        <v>5.06406</v>
       </c>
       <c r="I9" t="n">
-        <v>4.008</v>
+        <v>0.483</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
+        <v>45901</v>
+      </c>
+      <c r="B10" t="n">
+        <v>205.416</v>
+      </c>
+      <c r="C10" t="n">
+        <v>200.394719</v>
+      </c>
+      <c r="D10" t="n">
+        <v>76.643</v>
+      </c>
+      <c r="E10" t="n">
+        <v>9.42</v>
+      </c>
+      <c r="F10" t="n">
+        <v>40.297</v>
+      </c>
+      <c r="G10" t="n">
+        <v>33.73237</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.61244</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.684</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>45931</v>
+      </c>
+      <c r="B11" t="n">
+        <v>209.832</v>
+      </c>
+      <c r="C11" t="n">
+        <v>169.834281</v>
+      </c>
+      <c r="D11" t="n">
+        <v>78.235</v>
+      </c>
+      <c r="E11" t="n">
+        <v>33.222</v>
+      </c>
+      <c r="F11" t="n">
+        <v>52.457</v>
+      </c>
+      <c r="G11" t="n">
+        <v>35.03818</v>
+      </c>
+      <c r="H11" t="n">
+        <v>6.7747</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.19</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="B12" t="n">
+        <v>207.845</v>
+      </c>
+      <c r="C12" t="n">
+        <v>163.010029</v>
+      </c>
+      <c r="D12" t="n">
+        <v>85.893</v>
+      </c>
+      <c r="E12" t="n">
+        <v>45.654</v>
+      </c>
+      <c r="F12" t="n">
+        <v>56.861</v>
+      </c>
+      <c r="G12" t="n">
+        <v>32.26926</v>
+      </c>
+      <c r="H12" t="n">
+        <v>6.15653</v>
+      </c>
+      <c r="I12" t="n">
+        <v>4.008</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
         <v>45992</v>
       </c>
-      <c r="B10" t="n">
+      <c r="B13" t="n">
         <v>226.398</v>
       </c>
-      <c r="C10" t="n">
+      <c r="C13" t="n">
         <v>160.660302</v>
       </c>
-      <c r="D10" t="n">
+      <c r="D13" t="n">
         <v>99.19199999999999</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E13" t="n">
         <v>109.192</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F13" t="n">
         <v>30.811</v>
       </c>
-      <c r="G10" t="n">
+      <c r="G13" t="n">
         <v>34.40058999999999</v>
       </c>
-      <c r="H10" t="n">
+      <c r="H13" t="n">
         <v>8.43905</v>
       </c>
-      <c r="I10" t="n">
+      <c r="I13" t="n">
         <v>8.725999999999999</v>
       </c>
     </row>
@@ -1711,7 +1798,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1769,67 +1856,100 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>45778</v>
+        <v>45748</v>
       </c>
       <c r="B5" t="n">
-        <v>614.5458739999999</v>
+        <v>598.95957</v>
       </c>
       <c r="C5" t="n">
-        <v>535.16431</v>
+        <v>513.6627999999999</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>45809</v>
+        <v>45778</v>
       </c>
       <c r="B6" t="n">
-        <v>584.899145</v>
+        <v>614.5458739999999</v>
       </c>
       <c r="C6" t="n">
-        <v>499.78234</v>
+        <v>535.16431</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>45839</v>
+        <v>45809</v>
       </c>
       <c r="B7" t="n">
-        <v>572.843669</v>
+        <v>584.899145</v>
       </c>
       <c r="C7" t="n">
-        <v>493.33767</v>
+        <v>499.78234</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>45901</v>
+        <v>45839</v>
       </c>
       <c r="B8" t="n">
-        <v>570.199529</v>
+        <v>572.843669</v>
       </c>
       <c r="C8" t="n">
-        <v>488.22937</v>
+        <v>493.33767</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>45962</v>
+        <v>45870</v>
       </c>
       <c r="B9" t="n">
-        <v>601.696819</v>
+        <v>570.7191330000001</v>
       </c>
       <c r="C9" t="n">
-        <v>517.24855</v>
+        <v>485.35251</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
+        <v>45901</v>
+      </c>
+      <c r="B10" t="n">
+        <v>570.199529</v>
+      </c>
+      <c r="C10" t="n">
+        <v>488.22937</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>45931</v>
+      </c>
+      <c r="B11" t="n">
+        <v>587.583161</v>
+      </c>
+      <c r="C11" t="n">
+        <v>505.57168</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="B12" t="n">
+        <v>601.696819</v>
+      </c>
+      <c r="C12" t="n">
+        <v>517.24855</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
         <v>45992</v>
       </c>
-      <c r="B10" t="n">
+      <c r="B13" t="n">
         <v>677.818942</v>
       </c>
-      <c r="C10" t="n">
+      <c r="C13" t="n">
         <v>573.52428</v>
       </c>
     </row>
@@ -1845,7 +1965,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1945,121 +2065,181 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>45778</v>
+        <v>45748</v>
       </c>
       <c r="B5" t="n">
-        <v>2.80944</v>
+        <v>2.93977</v>
       </c>
       <c r="C5" t="n">
-        <v>4.960430000000001</v>
+        <v>4.74967</v>
       </c>
       <c r="D5" t="n">
-        <v>4.435899999999999</v>
+        <v>4.694649999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>18.751</v>
+        <v>15.884</v>
       </c>
       <c r="F5" t="n">
-        <v>15.12791</v>
+        <v>14.19029</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>45809</v>
+        <v>45778</v>
       </c>
       <c r="B6" t="n">
-        <v>3.15515</v>
+        <v>2.80944</v>
       </c>
       <c r="C6" t="n">
-        <v>4.58021</v>
+        <v>4.960430000000001</v>
       </c>
       <c r="D6" t="n">
-        <v>4.6374</v>
+        <v>4.435899999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>21.683</v>
+        <v>18.751</v>
       </c>
       <c r="F6" t="n">
-        <v>14.12432</v>
+        <v>15.12791</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>45839</v>
+        <v>45809</v>
       </c>
       <c r="B7" t="n">
-        <v>3.14177</v>
+        <v>3.15515</v>
       </c>
       <c r="C7" t="n">
-        <v>4.4663</v>
+        <v>4.58021</v>
       </c>
       <c r="D7" t="n">
-        <v>4.08026</v>
+        <v>4.6374</v>
       </c>
       <c r="E7" t="n">
-        <v>24.814</v>
+        <v>21.683</v>
       </c>
       <c r="F7" t="n">
-        <v>15.47851</v>
+        <v>14.12432</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>45901</v>
+        <v>45839</v>
       </c>
       <c r="B8" t="n">
-        <v>3.15928</v>
+        <v>3.14177</v>
       </c>
       <c r="C8" t="n">
-        <v>4.53209</v>
+        <v>4.4663</v>
       </c>
       <c r="D8" t="n">
-        <v>3.47733</v>
+        <v>4.08026</v>
       </c>
       <c r="E8" t="n">
-        <v>22.507</v>
+        <v>24.814</v>
       </c>
       <c r="F8" t="n">
-        <v>14.71027</v>
+        <v>15.47851</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>45962</v>
+        <v>45870</v>
       </c>
       <c r="B9" t="n">
-        <v>2.90993</v>
+        <v>3.23067</v>
       </c>
       <c r="C9" t="n">
-        <v>3.35135</v>
+        <v>5.16267</v>
       </c>
       <c r="D9" t="n">
-        <v>3.90887</v>
+        <v>3.38066</v>
       </c>
       <c r="E9" t="n">
-        <v>28.359</v>
+        <v>22.572</v>
       </c>
       <c r="F9" t="n">
-        <v>10.49435</v>
+        <v>15.27514</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
+        <v>45901</v>
+      </c>
+      <c r="B10" t="n">
+        <v>3.15928</v>
+      </c>
+      <c r="C10" t="n">
+        <v>4.53209</v>
+      </c>
+      <c r="D10" t="n">
+        <v>3.47733</v>
+      </c>
+      <c r="E10" t="n">
+        <v>22.507</v>
+      </c>
+      <c r="F10" t="n">
+        <v>14.71027</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>45931</v>
+      </c>
+      <c r="B11" t="n">
+        <v>2.13918</v>
+      </c>
+      <c r="C11" t="n">
+        <v>3.13387</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.97041</v>
+      </c>
+      <c r="E11" t="n">
+        <v>24.941</v>
+      </c>
+      <c r="F11" t="n">
+        <v>12.68071</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="B12" t="n">
+        <v>2.90993</v>
+      </c>
+      <c r="C12" t="n">
+        <v>3.35135</v>
+      </c>
+      <c r="D12" t="n">
+        <v>3.90887</v>
+      </c>
+      <c r="E12" t="n">
+        <v>28.359</v>
+      </c>
+      <c r="F12" t="n">
+        <v>10.49435</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
         <v>45992</v>
       </c>
-      <c r="B10" t="n">
+      <c r="B13" t="n">
         <v>2.7404</v>
       </c>
-      <c r="C10" t="n">
+      <c r="C13" t="n">
         <v>3.49538</v>
       </c>
-      <c r="D10" t="n">
+      <c r="D13" t="n">
         <v>4.0247</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E13" t="n">
         <v>34.323</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F13" t="n">
         <v>12.25567</v>
       </c>
     </row>
@@ -2075,7 +2255,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:L13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2263,240 +2443,360 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-05</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>218458</v>
+        <v>211461</v>
       </c>
       <c r="C5" t="n">
-        <v>77030</v>
+        <v>75415</v>
       </c>
       <c r="D5" t="n">
-        <v>34793.85</v>
+        <v>38601.6</v>
       </c>
       <c r="E5" t="n">
-        <v>3509</v>
+        <v>5146</v>
       </c>
       <c r="F5" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G5" t="n">
-        <v>128581.164</v>
+        <v>156538.31</v>
       </c>
       <c r="H5" t="n">
-        <v>73521</v>
+        <v>62194</v>
       </c>
       <c r="I5" t="n">
-        <v>1238.86</v>
+        <v>6089.66</v>
       </c>
       <c r="J5" t="n">
-        <v>75678</v>
+        <v>43505</v>
       </c>
       <c r="K5" t="n">
-        <v>1731</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>614545.874</v>
+        <v>598959.5699999999</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>215673</v>
+        <v>218458</v>
       </c>
       <c r="C6" t="n">
-        <v>85560</v>
+        <v>77030</v>
       </c>
       <c r="D6" t="n">
-        <v>26888.44</v>
+        <v>34793.85</v>
       </c>
       <c r="E6" t="n">
-        <v>1928</v>
+        <v>3509</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G6" t="n">
-        <v>124234.705</v>
+        <v>128581.164</v>
       </c>
       <c r="H6" t="n">
-        <v>71702</v>
+        <v>73521</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>1238.86</v>
       </c>
       <c r="J6" t="n">
-        <v>56997</v>
+        <v>75678</v>
       </c>
       <c r="K6" t="n">
-        <v>1916</v>
+        <v>1731</v>
       </c>
       <c r="L6" t="n">
-        <v>584899.145</v>
+        <v>614545.874</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>200388</v>
+        <v>215673</v>
       </c>
       <c r="C7" t="n">
-        <v>89746</v>
+        <v>85560</v>
       </c>
       <c r="D7" t="n">
-        <v>22694.23</v>
+        <v>26888.44</v>
       </c>
       <c r="E7" t="n">
-        <v>952</v>
+        <v>1928</v>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>144213.379</v>
+        <v>124234.705</v>
       </c>
       <c r="H7" t="n">
-        <v>52550</v>
+        <v>71702</v>
       </c>
       <c r="I7" t="n">
-        <v>758.0599999999999</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>60451</v>
+        <v>56997</v>
       </c>
       <c r="K7" t="n">
-        <v>1090</v>
+        <v>1916</v>
       </c>
       <c r="L7" t="n">
-        <v>572843.669</v>
+        <v>584899.145</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>205416</v>
+        <v>200388</v>
       </c>
       <c r="C8" t="n">
-        <v>76643</v>
+        <v>89746</v>
       </c>
       <c r="D8" t="n">
-        <v>33732.37</v>
+        <v>22694.23</v>
       </c>
       <c r="E8" t="n">
-        <v>1060</v>
+        <v>952</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G8" t="n">
-        <v>200394.719</v>
+        <v>144213.379</v>
       </c>
       <c r="H8" t="n">
-        <v>9420</v>
+        <v>52550</v>
       </c>
       <c r="I8" t="n">
-        <v>2612.44</v>
+        <v>758.0599999999999</v>
       </c>
       <c r="J8" t="n">
-        <v>40297</v>
+        <v>60451</v>
       </c>
       <c r="K8" t="n">
-        <v>624</v>
+        <v>1090</v>
       </c>
       <c r="L8" t="n">
-        <v>570199.529</v>
+        <v>572843.669</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-11</t>
+          <t>2025-08</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>207845</v>
+        <v>193413</v>
       </c>
       <c r="C9" t="n">
-        <v>85893</v>
+        <v>77164</v>
       </c>
       <c r="D9" t="n">
-        <v>32269.26</v>
+        <v>31029.29</v>
       </c>
       <c r="E9" t="n">
-        <v>2704</v>
+        <v>483</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>163010.029</v>
+        <v>190294.783</v>
       </c>
       <c r="H9" t="n">
-        <v>45654</v>
+        <v>21961</v>
       </c>
       <c r="I9" t="n">
-        <v>6156.53</v>
+        <v>5064.06</v>
       </c>
       <c r="J9" t="n">
-        <v>56861</v>
+        <v>51310</v>
       </c>
       <c r="K9" t="n">
-        <v>1304</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>601696.819</v>
+        <v>570719.133</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>2025-09</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>205416</v>
+      </c>
+      <c r="C10" t="n">
+        <v>76643</v>
+      </c>
+      <c r="D10" t="n">
+        <v>33732.37</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1060</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>200394.719</v>
+      </c>
+      <c r="H10" t="n">
+        <v>9420</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2612.44</v>
+      </c>
+      <c r="J10" t="n">
+        <v>40297</v>
+      </c>
+      <c r="K10" t="n">
+        <v>624</v>
+      </c>
+      <c r="L10" t="n">
+        <v>570199.529</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>209832</v>
+      </c>
+      <c r="C11" t="n">
+        <v>78235</v>
+      </c>
+      <c r="D11" t="n">
+        <v>35038.18</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1311</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>169834.281</v>
+      </c>
+      <c r="H11" t="n">
+        <v>33222</v>
+      </c>
+      <c r="I11" t="n">
+        <v>6774.7</v>
+      </c>
+      <c r="J11" t="n">
+        <v>52457</v>
+      </c>
+      <c r="K11" t="n">
+        <v>879</v>
+      </c>
+      <c r="L11" t="n">
+        <v>587583.161</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>207845</v>
+      </c>
+      <c r="C12" t="n">
+        <v>85893</v>
+      </c>
+      <c r="D12" t="n">
+        <v>32269.26</v>
+      </c>
+      <c r="E12" t="n">
+        <v>2704</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>163010.029</v>
+      </c>
+      <c r="H12" t="n">
+        <v>45654</v>
+      </c>
+      <c r="I12" t="n">
+        <v>6156.53</v>
+      </c>
+      <c r="J12" t="n">
+        <v>56861</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1304</v>
+      </c>
+      <c r="L12" t="n">
+        <v>601696.819</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>2025-12</t>
         </is>
       </c>
-      <c r="B10" t="n">
+      <c r="B13" t="n">
         <v>226398</v>
       </c>
-      <c r="C10" t="n">
+      <c r="C13" t="n">
         <v>99192</v>
       </c>
-      <c r="D10" t="n">
+      <c r="D13" t="n">
         <v>34400.59</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E13" t="n">
         <v>4648</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F13" t="n">
         <v>1</v>
       </c>
-      <c r="G10" t="n">
+      <c r="G13" t="n">
         <v>160660.302</v>
       </c>
-      <c r="H10" t="n">
+      <c r="H13" t="n">
         <v>109192</v>
       </c>
-      <c r="I10" t="n">
+      <c r="I13" t="n">
         <v>8439.049999999999</v>
       </c>
-      <c r="J10" t="n">
+      <c r="J13" t="n">
         <v>30811</v>
       </c>
-      <c r="K10" t="n">
+      <c r="K13" t="n">
         <v>4077</v>
       </c>
-      <c r="L10" t="n">
+      <c r="L13" t="n">
         <v>677818.942</v>
       </c>
     </row>
@@ -2511,7 +2811,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2587,96 +2887,144 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-05</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>500024.31</v>
+        <v>476258.8</v>
       </c>
       <c r="C5" t="n">
-        <v>35140</v>
+        <v>37404</v>
       </c>
       <c r="D5" t="n">
-        <v>535164.3100000001</v>
+        <v>513662.8</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>471176.34</v>
+        <v>500024.31</v>
       </c>
       <c r="C6" t="n">
-        <v>28606</v>
+        <v>35140</v>
       </c>
       <c r="D6" t="n">
-        <v>499782.34</v>
+        <v>535164.3100000001</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>467498.67</v>
+        <v>471176.34</v>
       </c>
       <c r="C7" t="n">
-        <v>25839</v>
+        <v>28606</v>
       </c>
       <c r="D7" t="n">
-        <v>493337.67</v>
+        <v>499782.34</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>454585.37</v>
+        <v>467498.67</v>
       </c>
       <c r="C8" t="n">
-        <v>33644</v>
+        <v>25839</v>
       </c>
       <c r="D8" t="n">
-        <v>488229.37</v>
+        <v>493337.67</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-11</t>
+          <t>2025-08</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>484569.55</v>
+        <v>453827.51</v>
       </c>
       <c r="C9" t="n">
-        <v>32679</v>
+        <v>31525</v>
       </c>
       <c r="D9" t="n">
-        <v>517248.55</v>
+        <v>485352.51</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>2025-09</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>454585.37</v>
+      </c>
+      <c r="C10" t="n">
+        <v>33644</v>
+      </c>
+      <c r="D10" t="n">
+        <v>488229.37</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>470121.68</v>
+      </c>
+      <c r="C11" t="n">
+        <v>35450</v>
+      </c>
+      <c r="D11" t="n">
+        <v>505571.68</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>484569.55</v>
+      </c>
+      <c r="C12" t="n">
+        <v>32679</v>
+      </c>
+      <c r="D12" t="n">
+        <v>517248.55</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>2025-12</t>
         </is>
       </c>
-      <c r="B10" t="n">
+      <c r="B13" t="n">
         <v>538489.28</v>
       </c>
-      <c r="C10" t="n">
+      <c r="C13" t="n">
         <v>35035</v>
       </c>
-      <c r="D10" t="n">
+      <c r="D13" t="n">
         <v>573524.28</v>
       </c>
     </row>
@@ -2691,7 +3039,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2809,150 +3157,225 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-05</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2809.44</v>
+        <v>2939.77</v>
       </c>
       <c r="C5" t="n">
-        <v>4960.43</v>
+        <v>4749.67</v>
       </c>
       <c r="D5" t="n">
-        <v>4435.9</v>
+        <v>4694.65</v>
       </c>
       <c r="E5" t="n">
-        <v>18751</v>
+        <v>15884</v>
       </c>
       <c r="F5" t="n">
-        <v>15127.91</v>
+        <v>14190.29</v>
       </c>
       <c r="G5" t="n">
-        <v>46084.68</v>
+        <v>42458.38</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3155.15</v>
+        <v>2809.44</v>
       </c>
       <c r="C6" t="n">
-        <v>4580.21</v>
+        <v>4960.43</v>
       </c>
       <c r="D6" t="n">
-        <v>4637.4</v>
+        <v>4435.9</v>
       </c>
       <c r="E6" t="n">
-        <v>21683</v>
+        <v>18751</v>
       </c>
       <c r="F6" t="n">
-        <v>14124.32</v>
+        <v>15127.91</v>
       </c>
       <c r="G6" t="n">
-        <v>48180.08</v>
+        <v>46084.68</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3141.77</v>
+        <v>3155.15</v>
       </c>
       <c r="C7" t="n">
-        <v>4466.3</v>
+        <v>4580.21</v>
       </c>
       <c r="D7" t="n">
-        <v>4080.26</v>
+        <v>4637.4</v>
       </c>
       <c r="E7" t="n">
-        <v>24814</v>
+        <v>21683</v>
       </c>
       <c r="F7" t="n">
-        <v>15478.51</v>
+        <v>14124.32</v>
       </c>
       <c r="G7" t="n">
-        <v>51980.84</v>
+        <v>48180.08</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3159.28</v>
+        <v>3141.77</v>
       </c>
       <c r="C8" t="n">
-        <v>4532.09</v>
+        <v>4466.3</v>
       </c>
       <c r="D8" t="n">
-        <v>3477.33</v>
+        <v>4080.26</v>
       </c>
       <c r="E8" t="n">
-        <v>22507</v>
+        <v>24814</v>
       </c>
       <c r="F8" t="n">
-        <v>14710.27</v>
+        <v>15478.51</v>
       </c>
       <c r="G8" t="n">
-        <v>48385.97</v>
+        <v>51980.84</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-11</t>
+          <t>2025-08</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2909.93</v>
+        <v>3230.67</v>
       </c>
       <c r="C9" t="n">
-        <v>3351.35</v>
+        <v>5162.67</v>
       </c>
       <c r="D9" t="n">
-        <v>3908.87</v>
+        <v>3380.66</v>
       </c>
       <c r="E9" t="n">
-        <v>28359</v>
+        <v>22572</v>
       </c>
       <c r="F9" t="n">
-        <v>10494.35</v>
+        <v>15275.14</v>
       </c>
       <c r="G9" t="n">
-        <v>49023.5</v>
+        <v>49621.14</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>2025-09</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>3159.28</v>
+      </c>
+      <c r="C10" t="n">
+        <v>4532.09</v>
+      </c>
+      <c r="D10" t="n">
+        <v>3477.33</v>
+      </c>
+      <c r="E10" t="n">
+        <v>22507</v>
+      </c>
+      <c r="F10" t="n">
+        <v>14710.27</v>
+      </c>
+      <c r="G10" t="n">
+        <v>48385.97</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>2139.18</v>
+      </c>
+      <c r="C11" t="n">
+        <v>3133.87</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2970.41</v>
+      </c>
+      <c r="E11" t="n">
+        <v>24941</v>
+      </c>
+      <c r="F11" t="n">
+        <v>12680.71</v>
+      </c>
+      <c r="G11" t="n">
+        <v>45865.17</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>2909.93</v>
+      </c>
+      <c r="C12" t="n">
+        <v>3351.35</v>
+      </c>
+      <c r="D12" t="n">
+        <v>3908.87</v>
+      </c>
+      <c r="E12" t="n">
+        <v>28359</v>
+      </c>
+      <c r="F12" t="n">
+        <v>10494.35</v>
+      </c>
+      <c r="G12" t="n">
+        <v>49023.5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>2025-12</t>
         </is>
       </c>
-      <c r="B10" t="n">
+      <c r="B13" t="n">
         <v>2740.4</v>
       </c>
-      <c r="C10" t="n">
+      <c r="C13" t="n">
         <v>3495.38</v>
       </c>
-      <c r="D10" t="n">
+      <c r="D13" t="n">
         <v>4024.7</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E13" t="n">
         <v>34323</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F13" t="n">
         <v>12255.67</v>
       </c>
-      <c r="G10" t="n">
+      <c r="G13" t="n">
         <v>56839.15</v>
       </c>
     </row>
@@ -2967,7 +3390,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3145,26 +3568,26 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-05</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>333795.85</v>
+        <v>330632.6</v>
       </c>
       <c r="C5" t="n">
-        <v>333795.85</v>
+        <v>330632.6</v>
       </c>
       <c r="D5" t="n">
-        <v>280750.024</v>
+        <v>268326.97</v>
       </c>
       <c r="E5" t="n">
-        <v>280750.02</v>
+        <v>268326.97</v>
       </c>
       <c r="F5" t="n">
-        <v>46084.68</v>
+        <v>42458.38</v>
       </c>
       <c r="G5" t="n">
-        <v>46084.67</v>
+        <v>42458.39</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -3185,26 +3608,26 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>330049.44</v>
+        <v>333795.85</v>
       </c>
       <c r="C6" t="n">
-        <v>330049.45</v>
+        <v>333795.85</v>
       </c>
       <c r="D6" t="n">
-        <v>254849.705</v>
+        <v>280750.024</v>
       </c>
       <c r="E6" t="n">
-        <v>254849.71</v>
+        <v>280750.02</v>
       </c>
       <c r="F6" t="n">
-        <v>48180.08</v>
+        <v>46084.68</v>
       </c>
       <c r="G6" t="n">
-        <v>48180.08</v>
+        <v>46084.67</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -3225,23 +3648,26 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>313781.23</v>
+        <v>330049.44</v>
       </c>
       <c r="C7" t="n">
-        <v>313781.22</v>
+        <v>330049.45</v>
       </c>
       <c r="D7" t="n">
-        <v>259062.439</v>
+        <v>254849.705</v>
       </c>
       <c r="E7" t="n">
-        <v>259062.44</v>
+        <v>254849.71</v>
       </c>
       <c r="F7" t="n">
-        <v>51980.84</v>
+        <v>48180.08</v>
+      </c>
+      <c r="G7" t="n">
+        <v>48180.08</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -3262,26 +3688,23 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>316851.37</v>
+        <v>313781.23</v>
       </c>
       <c r="C8" t="n">
-        <v>316851.36</v>
+        <v>313781.22</v>
       </c>
       <c r="D8" t="n">
-        <v>253348.159</v>
+        <v>259062.439</v>
       </c>
       <c r="E8" t="n">
-        <v>253348.16</v>
+        <v>259062.44</v>
       </c>
       <c r="F8" t="n">
-        <v>48385.97</v>
-      </c>
-      <c r="G8" t="n">
-        <v>48385.97</v>
+        <v>51980.84</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -3302,26 +3725,23 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-11</t>
+          <t>2025-08</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>328711.26</v>
+        <v>302089.29</v>
       </c>
       <c r="C9" t="n">
-        <v>328711.25</v>
+        <v>302089.29</v>
       </c>
       <c r="D9" t="n">
-        <v>272985.559</v>
+        <v>268629.843</v>
       </c>
       <c r="E9" t="n">
-        <v>272985.55</v>
+        <v>268629.84</v>
       </c>
       <c r="F9" t="n">
-        <v>49023.5</v>
-      </c>
-      <c r="G9" t="n">
-        <v>49023.51</v>
+        <v>49621.14</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -3342,38 +3762,158 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>2025-09</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>316851.37</v>
+      </c>
+      <c r="C10" t="n">
+        <v>316851.36</v>
+      </c>
+      <c r="D10" t="n">
+        <v>253348.159</v>
+      </c>
+      <c r="E10" t="n">
+        <v>253348.16</v>
+      </c>
+      <c r="F10" t="n">
+        <v>48385.97</v>
+      </c>
+      <c r="G10" t="n">
+        <v>48385.97</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>324416.1800000001</v>
+      </c>
+      <c r="C11" t="n">
+        <v>324416.18</v>
+      </c>
+      <c r="D11" t="n">
+        <v>263166.981</v>
+      </c>
+      <c r="E11" t="n">
+        <v>263166.98</v>
+      </c>
+      <c r="F11" t="n">
+        <v>45865.17</v>
+      </c>
+      <c r="G11" t="n">
+        <v>45865.17</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>328711.26</v>
+      </c>
+      <c r="C12" t="n">
+        <v>328711.25</v>
+      </c>
+      <c r="D12" t="n">
+        <v>272985.559</v>
+      </c>
+      <c r="E12" t="n">
+        <v>272985.55</v>
+      </c>
+      <c r="F12" t="n">
+        <v>49023.5</v>
+      </c>
+      <c r="G12" t="n">
+        <v>49023.51</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>2025-12</t>
         </is>
       </c>
-      <c r="B10" t="n">
+      <c r="B13" t="n">
         <v>364639.59</v>
       </c>
-      <c r="C10" t="n">
+      <c r="C13" t="n">
         <v>364639.59</v>
       </c>
-      <c r="D10" t="n">
+      <c r="D13" t="n">
         <v>313179.352</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E13" t="n">
         <v>313179.35</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F13" t="n">
         <v>56839.15</v>
       </c>
-      <c r="G10" t="n">
+      <c r="G13" t="n">
         <v>56839.16</v>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -3390,7 +3930,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3498,148 +4038,223 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-05</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>https://arsel-cm.org/wp-content/uploads/2026/02/PV-de-validation-du-bilan-energetique-Mai-2025.pdf</t>
+          <t>https://arsel-cm.org/wp-content/uploads/2026/02/PV-de-validation-du-bilan-ener-getique-Avril-2025_V2_GOOD.pdf</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2259358</v>
+        <v>2324105</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Tue, 17 Feb 2026 18:32:05 GMT</t>
+          <t>Tue, 17 Feb 2026 18:31:58 GMT</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-02-11T16:00:07</t>
+          <t>2026-02-11T15:59:45</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>https://arsel-cm.org/wp-content/uploads/2026/02/PV-de-validation-du-bilan-en-ergetique-Juin-2025_BON.pdf</t>
+          <t>https://arsel-cm.org/wp-content/uploads/2026/02/PV-de-validation-du-bilan-energetique-Mai-2025.pdf</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2239541</v>
+        <v>2259358</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Tue, 17 Feb 2026 18:31:36 GMT</t>
+          <t>Tue, 17 Feb 2026 18:32:05 GMT</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-02-11T16:01:00</t>
+          <t>2026-02-11T16:00:07</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>https://arsel-cm.org/wp-content/uploads/2026/02/PV-de-validation-du-bilan-e-nergetique-Juillet-2025.pdf</t>
+          <t>https://arsel-cm.org/wp-content/uploads/2026/02/PV-de-validation-du-bilan-en-ergetique-Juin-2025_BON.pdf</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2207975</v>
+        <v>2239541</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Tue, 17 Feb 2026 18:31:26 GMT</t>
+          <t>Tue, 17 Feb 2026 18:31:36 GMT</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-02-11T15:58:13</t>
+          <t>2026-02-11T16:01:00</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>https://arsel-cm.org/wp-content/uploads/2026/02/PV-de-validation-du-bilan-en-ergetique-Septembre-2025.pdf</t>
+          <t>https://arsel-cm.org/wp-content/uploads/2026/02/PV-de-validation-du-bilan-e-nergetique-Juillet-2025.pdf</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2330332</v>
+        <v>2207975</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Tue, 17 Feb 2026 18:31:46 GMT</t>
+          <t>Tue, 17 Feb 2026 18:31:26 GMT</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-02-11T16:00:43</t>
+          <t>2026-02-11T15:58:13</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-11</t>
+          <t>2025-08</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>https://arsel-cm.org/wp-content/uploads/2026/02/PV-de-validation-du-bilan-en-ergetique-Novembre-2025.pdf</t>
+          <t>https://arsel-cm.org/wp-content/uploads/2026/02/PV-de-validation-du-bilan-energetique-Aout-2025.pdf</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2174160</v>
+        <v>2291058</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Tue, 17 Feb 2026 18:31:43 GMT</t>
+          <t>Tue, 17 Feb 2026 18:31:59 GMT</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-02-11T15:57:58</t>
+          <t>2026-02-11T15:59:10</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>2025-09</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>https://arsel-cm.org/wp-content/uploads/2026/02/PV-de-validation-du-bilan-en-ergetique-Septembre-2025.pdf</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>2330332</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Tue, 17 Feb 2026 18:31:46 GMT</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>2026-02-11T16:00:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>https://arsel-cm.org/wp-content/uploads/2026/02/PV-de-validation-du-bilan-ene-rgetique-Octobre-20251.pdf</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>2275580</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Tue, 17 Feb 2026 18:31:51 GMT</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>2026-02-11T16:00:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>https://arsel-cm.org/wp-content/uploads/2026/02/PV-de-validation-du-bilan-en-ergetique-Novembre-2025.pdf</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>2174160</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Tue, 17 Feb 2026 18:31:43 GMT</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>2026-02-11T15:57:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>2025-12</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>https://arsel-cm.org/wp-content/uploads/2026/02/PV-de-validation-du-bilan-en-ergetique-Decembre-2025.pdf</t>
         </is>
       </c>
-      <c r="C10" t="n">
+      <c r="C13" t="n">
         <v>2232766</v>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>Tue, 17 Feb 2026 18:31:31 GMT</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>2026-02-11T15:58:28</t>
         </is>
